--- a/public/bulk_product_upload_sample.xlsx
+++ b/public/bulk_product_upload_sample.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +30,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -39,39 +38,21 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002E75B6"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -80,36 +61,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -117,56 +73,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,31 +461,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="65" customWidth="1" min="18" max="18"/>
-    <col width="65" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
+    <col width="70" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>product_name</t>
@@ -567,12 +496,12 @@
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -582,7 +511,7 @@
           <t>sku</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mpn</t>
         </is>
@@ -592,94 +521,94 @@
           <t>description</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>highlights</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>featured</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>top_selling</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>new_arrival</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>image_1</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>image_2</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>image_3</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>specs_1</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>specs_2</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Samsung Galaxy S24 Ultra</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Smartphones</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>SAM-S24U-256</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SAM-S24U-256</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>SM-S928BZKGEUB</t>
         </is>
@@ -694,45 +623,45 @@
           <t>200MP Camera | Snapdragon 8 Gen 3 | 5000mAh Battery | S Pen included | Titanium frame</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="2" t="n">
         <v>149999</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>50</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/s24ultra_front.jpg</t>
+          <t>https://picsum.photos/seed/samsung-s24-front/600/600.jpg</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/s24ultra_back.jpg</t>
+          <t>https://picsum.photos/seed/samsung-s24-back/600/600.jpg</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/s24ultra_side.jpg</t>
+          <t>https://picsum.photos/seed/samsung-s24-side/600/600.jpg</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -746,122 +675,122 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Apple MacBook Pro 14-inch M3</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Laptops</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>APL-MBP14-M3-512</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>TEST-APL-MBP14-M3-512</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>MR7J3LL/A</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>MacBook Pro 14-inch with M3 chip delivers exceptional performance with a stunning Liquid Retina XDR display, up to 18 hours of battery life.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>M3 Chip | 14-inch Liquid Retina XDR | 18hr Battery | 16GB Unified Memory | 512GB SSD</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="2" t="n">
         <v>199900</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="n">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/mbp14_silver.jpg</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/mbp14_open.jpg</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/macbook-pro-silver/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/macbook-pro-open/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>General:Display=14.2-inch Liquid Retina XDR|Resolution=3024x1964|Processor=Apple M3;Memory:RAM=16GB Unified|Storage=512GB SSD|SSD Speed=7.4GB/s</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Connectivity:USB-C=3x Thunderbolt 4|HDMI=1x HDMI 2.1|SD Card=SDXC;Battery:Life=Up to 18 hours|Capacity=70Wh</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>LG 1.5 Ton 5 Star Inverter Split AC</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Home Appliances</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Air Conditioners</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>LG-AC15-5ST-INV</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TEST-LG-AC15-5ST-INV</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PS-Q19YNZE</t>
         </is>
@@ -876,40 +805,40 @@
           <t>5 Star Rating | DUAL Inverter | Wi-Fi Control | Auto Cleaning | Ocean Black Protection</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
         <v>15</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/lg_ac_front.jpg</t>
+          <t>https://picsum.photos/seed/lg-ac-front/600/600.jpg</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/lg_ac_remote.jpg</t>
+          <t>https://picsum.photos/seed/lg-ac-remote/600/600.jpg</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -924,118 +853,118 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Nike Air Max 270 Running Shoes</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Fashion</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Footwear</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Nike</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>NIKE-AM270-BLK-10</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TEST-NIKE-AM270-BLK-10</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>AH8050-002</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Nike Air Max 270 features Nike's biggest heel Air unit yet for a super-soft ride that feels as impossible as it looks. Knit upper provides breathability and comfort.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Largest Air heel unit | Knit upper | Foam midsole | Durable rubber outsole</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="2" t="n">
         <v>12995</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/nike_am270_side.jpg</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/nike_am270_top.jpg</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/nike_am270_sole.jpg</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/nike-airmax-side/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/nike-airmax-top/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/nike-airmax-sole/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>General:Type=Running Shoe|Brand=Nike|Model=Air Max 270|Color=Black/White;Size:UK=10|US=11|EU=45</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Materials:Upper=Knit Fabric|Midsole=Foam + Air|Outsole=Rubber;Care:Washing=Hand Wash|Drying=Air Dry</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Generic USB-C Hub 7-in-1</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>USB-HUB-7IN1-GRY</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>TEST-USB-HUB-7IN1-GRY</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>7-in-1 USB-C hub with 4K HDMI, 3x USB 3.0, SD/TF card reader, and 100W PD charging. Compatible with MacBook, iPad Pro, and Windows laptops.</t>
@@ -1046,35 +975,35 @@
           <t>4K HDMI | 3x USB 3.0 | 100W PD | SD + TF Reader | Plug and Play</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/images/usb_hub_grey.jpg</t>
+          <t>https://picsum.photos/seed/usb-hub-grey/600/600.jpg</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
@@ -1085,6 +1014,277 @@
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sony WH-1000XM5 Wireless Headphones</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SONY-WH1000XM5-BLK</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>WH1000XM5/B</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Industry-leading noise cancellation with Auto NC Optimizer. Crystal clear hands-free calling and Alexa voice control. Up to 30-hour battery life with quick charging.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Industry-leading ANC | 30hr Battery | Multipoint Connection | LDAC Hi-Res Audio | Quick Charge</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>29990</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/sony-headphones-front/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/sony-headphones-folded/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>General:Type=Over-Ear|Connectivity=Bluetooth 5.2|Driver=30mm;Audio:Codec=LDAC|Frequency Response=4Hz-40kHz|Impedance=48 ohms</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Battery:Life=30 hours|Quick Charge=3 min for 3 hours|Charging Port=USB-C;Features:ANC=Yes|Touch Controls=Yes|Voice Assistant=Alexa/Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Boat Airdopes 141 TWS Earbuds</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Boat</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>TEST-BOAT-AD141-WHT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>BTAD141</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>boAt Airdopes 141 with 42 hours total playback, ENx Technology for clear calls, IPX4 water resistance, and BEAST Mode for low latency gaming.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>42hr Playtime | ENx Tech | IPX4 Rated | BEAST Mode | ASAP Charge</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/boat-earbuds-case/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/boat-earbuds-buds/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>General:Type=TWS Earbuds|Driver=8mm|Bluetooth=5.1;Battery:Earbuds=8hr|Case=42hr Total|Charging=Type-C</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Features:ENx Tech=Yes|IPX4=Water Resistant|Touch Controls=Yes|Voice Assistant=Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Adidas Ultraboost 22 Running Shoes</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>TEST-ADI-UB22-BLK-9</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>GZ0127</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Adidas Ultraboost 22 with responsive BOOST midsole, Primeknit+ upper that adapts to your foot, and Stretchweb outsole for flexible push-off.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>BOOST Midsole | Primeknit+ Upper | Continental Rubber | Linear Energy Push | Sustainable Materials</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>17999</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/adidas-ub-side/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/adidas-ub-top/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/seed/adidas-ub-sole/600/600.jpg</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>General:Type=Running Shoe|Brand=Adidas|Model=Ultraboost 22|Color=Core Black;Size:UK=9|US=9.5|EU=43</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>Materials:Upper=Primeknit+|Midsole=BOOST Foam|Outsole=Continental Rubber;Sustainability:Recycled Content=50%+</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1097,392 +1297,426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Bulk Product Upload – Field Reference Guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Sheet name must be exactly:  Products</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Bulk Product Upload — Field Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Sheet name must be exactly: Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Description &amp; Accepted Values</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Full product name. Max 255 characters.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Exact category name as it exists in the system. Case-insensitive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Exact category name. Created automatically if it does not exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Exact subcategory name. Leave blank if not applicable.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Exact brand name. Leave blank if unknown/generic.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Unique Stock Keeping Unit code. Must be unique across all products.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Unique Stock Keeping Unit code. Must be unique across ALL products in the database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>mpn</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Manufacturer Part Number.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Full product description. HTML tags are stripped server-side.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>highlights</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Short bullet points separated by ' | ' (pipe). E.g. 200MP Camera | 5000mAh Battery</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Numeric value only, no currency symbol. E.g. 14999.00</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>featured</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Boolean flag. Accepted: true / false / yes / no / 1 / 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Boolean. Accepted: true / false / yes / no / 1 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>top_selling</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Boolean flag. Accepted: true / false / yes / no / 1 / 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Boolean. Accepted: true / false / yes / no / 1 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>new_arrival</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Boolean flag. Accepted: true / false / yes / no / 1 / 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Boolean. Accepted: true / false / yes / no / 1 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Boolean flag. Defaults to true if left blank. Accepted: true / false / yes / no / 1 / 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Boolean. Defaults to true if blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Integer quantity available in inventory. E.g. 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Integer quantity. E.g. 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>image_1</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Publicly accessible URL to product image. JPEG/PNG recommended.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Publicly reachable HTTPS URL to product image. Must return Content-Type: image/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>image_2</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Second product image URL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Second product image URL. Same rules as image_1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>image_3</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Third product image URL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Third product image URL. Same rules as image_1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>specs_1</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Specifications string. Format: "Section:key1=val1|key2=val2;Section2:key3=val3"
-Example: General:Color=Black|Weight=185g;Camera:Main=200MP|Front=12MP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Specifications. Format: Section:key1=val1|key2=val2;Section2:key3=val3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>specs_2</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Additional specifications string. Same format as specs_1.
-Example: Battery:Capacity=5000mAh|Charging=45W;Connectivity:WiFi=WiFi 6E|Bluetooth=5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Specs Format Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>specs_1 value →</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>General:Display=6.8-inch|RAM=12GB;Camera:Main=200MP|Front=12MP|Video=8K@30fps</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Additional specifications. Same format as specs_1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>1. SKUs in this template start with TEST- to avoid clashing with previously uploaded data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2. Image URLs in this template use picsum.photos with deterministic seeds — they always return real JPEG images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>3. Replace these URLs with your actual product image URLs before going to production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>4. URLs must point to public HTTPS endpoints reachable from your server. Private IPs (10.x, 192.168.x) are blocked for security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>5. If you upload local image files via the multipart 'images' field, put the filename (e.g. samsung_front.jpg) in the image_N cell instead of a URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>6. Specs format: Section:key=value pairs joined by | (pipe), sections separated by ; (semicolon). Spaces around operators are trimmed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B26:C26"/>
+  <mergeCells count="7">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
